--- a/db/A7XLK-4107-AntiEpidemic.xlsx
+++ b/db/A7XLK-4107-AntiEpidemic.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10410"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10507"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1BCAB17-F21F-E947-8687-275882F54871}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6556481-2CCF-FC4F-AC39-0E4FD670F7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1480" yWindow="2400" windowWidth="27920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5380" yWindow="3840" windowWidth="27920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shopping" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
   <si>
     <t>title</t>
   </si>
@@ -192,10 +192,6 @@
   </si>
   <si>
     <t>週一至週五，9:30-12:00 13:00-18:30</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>桃園市</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -309,7 +305,99 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve"> 0925-704-305</t>
+    <t>生鮮食材</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防疫藥品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-412-Epidemic/XLK-412-Epidemic-61.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>301</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>雙寶居家保健生活館</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.bb-homecare.com/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>0925-704-305</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-2671-2002</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 週二~週六10:00-19:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>302</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>杏一醫療用品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台北市中山區民權東路二段70號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">林口長庚醫院復健大樓 </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-318-5247</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:00-22:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.medfirst.com.tw/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-412-Epidemic/XLK-412-Epidemic-62.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>蝦皮商城</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>303</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://shopee.tw/traceofwind3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>fig/XLK-412-Epidemic/XLK-412-Epidemic-63.jpeg</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市龜山區長慶三街40號1樓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-6636-6559</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:30-22:00</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -684,7 +772,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="2"/>
@@ -747,7 +835,7 @@
         <v>17</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -773,7 +861,7 @@
         <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
@@ -799,7 +887,7 @@
         <v>29</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -822,82 +910,82 @@
         <v>38</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>45</v>
-      </c>
       <c r="G6" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="E7" s="5" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>61</v>
-      </c>
       <c r="F8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
@@ -923,53 +1011,131 @@
         <v>10</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="E10" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="1" t="s">
-        <v>67</v>
-      </c>
       <c r="F10" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="D11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="H11" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>42</v>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -986,6 +1152,9 @@
     <hyperlink ref="G9" r:id="rId9" xr:uid="{57A9CA66-505B-594F-AF8A-046EE0124A18}"/>
     <hyperlink ref="G10" r:id="rId10" xr:uid="{AF74A568-1BF6-BB47-BC7F-44F4C9E38518}"/>
     <hyperlink ref="G11" r:id="rId11" xr:uid="{49A713EC-B681-6D47-86A3-2930538A10BD}"/>
+    <hyperlink ref="G12" r:id="rId12" xr:uid="{B95913EF-857B-904C-B92B-53EA148302F0}"/>
+    <hyperlink ref="G13" r:id="rId13" xr:uid="{1B2D31A2-127D-1341-8A39-A4B8C1FABE01}"/>
+    <hyperlink ref="G14" r:id="rId14" xr:uid="{2C3AED09-7731-8044-B64E-D8377B0E50D7}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>

--- a/db/A7XLK-4107-AntiEpidemic.xlsx
+++ b/db/A7XLK-4107-AntiEpidemic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6556481-2CCF-FC4F-AC39-0E4FD670F7B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB0DE573-B3AB-214D-96F3-ECD76CD2536B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5380" yWindow="3840" windowWidth="27920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4160" yWindow="1520" windowWidth="27920" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Shopping" sheetId="2" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="108">
   <si>
     <t>title</t>
   </si>
@@ -345,10 +345,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>杏一醫療用品</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>台北市中山區民權東路二段70號</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -398,6 +394,58 @@
   </si>
   <si>
     <t>10:30-22:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>304</t>
+  </si>
+  <si>
+    <t>305</t>
+  </si>
+  <si>
+    <t>fig/XLK-412-Epidemic/XLK-412-Epidemic-64.jpeg</t>
+  </si>
+  <si>
+    <t>fig/XLK-412-Epidemic/XLK-412-Epidemic-65.jpeg</t>
+  </si>
+  <si>
+    <t>佑全藥局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>杏一藥局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>丁丁藥局</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>http://www.yourchance.com.tw/index.php?lang=cht</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>桃園市大有路556號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>03-346-0793</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.norbelbaby.com.tw/TinTin/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>新北市林口區仁愛路二段128號1F</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>02-8601-8655</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>09:00-22:55</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -772,7 +820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.83203125" style="2"/>
@@ -1068,7 +1116,7 @@
         <v>75</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>78</v>
@@ -1091,22 +1139,22 @@
         <v>80</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="F13" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>85</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>86</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>72</v>
@@ -1114,27 +1162,79 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H14" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>72</v>
       </c>
     </row>
@@ -1154,7 +1254,9 @@
     <hyperlink ref="G11" r:id="rId11" xr:uid="{49A713EC-B681-6D47-86A3-2930538A10BD}"/>
     <hyperlink ref="G12" r:id="rId12" xr:uid="{B95913EF-857B-904C-B92B-53EA148302F0}"/>
     <hyperlink ref="G13" r:id="rId13" xr:uid="{1B2D31A2-127D-1341-8A39-A4B8C1FABE01}"/>
-    <hyperlink ref="G14" r:id="rId14" xr:uid="{2C3AED09-7731-8044-B64E-D8377B0E50D7}"/>
+    <hyperlink ref="G16" r:id="rId14" xr:uid="{2C3AED09-7731-8044-B64E-D8377B0E50D7}"/>
+    <hyperlink ref="G14" r:id="rId15" xr:uid="{94AA4F9F-21F7-8447-AAAE-4DC642015D19}"/>
+    <hyperlink ref="G15" r:id="rId16" xr:uid="{F1BE1257-F350-9A4A-AFCB-CFFC8D9B9FC7}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <pageSetup orientation="portrait"/>
